--- a/NECP Scenario/Results/Regional Results/SKYROS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/SKYROS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.335035615147384E-08</v>
+        <v>4.919265312950091E-08</v>
       </c>
       <c r="C3">
-        <v>1.918727058282095E-08</v>
+        <v>2.829914674457308E-08</v>
       </c>
       <c r="D3">
-        <v>0.005533453055858512</v>
+        <v>0.005539994886874022</v>
       </c>
       <c r="E3">
-        <v>0.7005756025800204</v>
+        <v>0.7908056212937384</v>
       </c>
       <c r="F3">
-        <v>0.8257601652862163</v>
+        <v>0.9451920569714017</v>
       </c>
       <c r="G3">
-        <v>0.8763212595839197</v>
+        <v>1.040556076107498</v>
       </c>
       <c r="H3">
-        <v>0.8995068337931024</v>
+        <v>0.9690980590623599</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.834780273097461E-08</v>
+        <v>4.181375516187582E-08</v>
       </c>
       <c r="C4">
-        <v>1.630917999761965E-08</v>
+        <v>2.405427473468719E-08</v>
       </c>
       <c r="D4">
-        <v>0.004703435097479719</v>
+        <v>0.004708995653843446</v>
       </c>
       <c r="E4">
-        <v>0.5954892621991091</v>
+        <v>0.6721847780995696</v>
       </c>
       <c r="F4">
-        <v>0.7018961404902916</v>
+        <v>0.8034132484252966</v>
       </c>
       <c r="G4">
-        <v>0.7448730706464598</v>
+        <v>0.8844726646910651</v>
       </c>
       <c r="H4">
-        <v>0.7645808087238666</v>
+        <v>0.8237333502030117</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.01408635719975653</v>
+        <v>0.01408635831170917</v>
       </c>
       <c r="C14">
-        <v>0.01598891724599047</v>
+        <v>0.01598891773610169</v>
       </c>
       <c r="D14">
-        <v>0.01761586176971418</v>
+        <v>0.01761585197879624</v>
       </c>
       <c r="E14">
-        <v>0.0165225853283564</v>
+        <v>0.01652259901645899</v>
       </c>
       <c r="F14">
-        <v>0.02100516322661529</v>
+        <v>0.02100518936336162</v>
       </c>
       <c r="G14">
-        <v>0.02582247733954426</v>
+        <v>0.02582251635466754</v>
       </c>
       <c r="H14">
-        <v>0.03357314811639185</v>
+        <v>0.03357335990807379</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.04888187568662922</v>
+        <v>0.04888189220042023</v>
       </c>
       <c r="C28">
-        <v>0.05571554832505227</v>
+        <v>0.05571555671859358</v>
       </c>
       <c r="D28">
-        <v>0.006651904014902022</v>
+        <v>0.00665507647513131</v>
       </c>
       <c r="E28">
-        <v>3.919771825602332E-08</v>
+        <v>5.813441409185293E-08</v>
       </c>
       <c r="F28">
-        <v>4.081615648315806E-08</v>
+        <v>6.031295469055228E-08</v>
       </c>
       <c r="G28">
-        <v>4.672667321414272E-08</v>
+        <v>6.920946821934626E-08</v>
       </c>
       <c r="H28">
-        <v>4.86105790565829E-05</v>
+        <v>3.876080609950496E-07</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.01388689649202143</v>
+        <v>0.01388690117873916</v>
       </c>
       <c r="C29">
-        <v>0.01582828076900446</v>
+        <v>0.01582828315107254</v>
       </c>
       <c r="D29">
-        <v>0.001889745451191602</v>
+        <v>0.001890646714684962</v>
       </c>
       <c r="E29">
-        <v>1.112455854136558E-08</v>
+        <v>1.649898502462425E-08</v>
       </c>
       <c r="F29">
-        <v>1.157909521893959E-08</v>
+        <v>1.7110143595948E-08</v>
       </c>
       <c r="G29">
-        <v>1.32505060014483E-08</v>
+        <v>1.962617709755769E-08</v>
       </c>
       <c r="H29">
-        <v>1.380967730673807E-05</v>
+        <v>1.099000192398066E-07</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.007134024127437997</v>
+        <v>0.007128015561635356</v>
       </c>
       <c r="E30">
-        <v>0.09511829029319421</v>
+        <v>0.09503311560635602</v>
       </c>
       <c r="F30">
-        <v>0.09511764926940712</v>
+        <v>0.094972285169243</v>
       </c>
       <c r="G30">
-        <v>0.09511681492878341</v>
+        <v>0.09501491303546949</v>
       </c>
       <c r="H30">
-        <v>0.09510470981304014</v>
+        <v>0.09508565966930851</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.0004869424223128039</v>
+        <v>0.0004869412630420252</v>
       </c>
       <c r="C31">
-        <v>0.0004869438066892772</v>
+        <v>0.0004869433001224435</v>
       </c>
       <c r="D31">
-        <v>0.0004699954461088853</v>
+        <v>0.0004697484052155765</v>
       </c>
       <c r="E31">
-        <v>0.0004859641314466046</v>
+        <v>0.0004846766110153246</v>
       </c>
       <c r="F31">
-        <v>0.0004854487117308311</v>
+        <v>0.0004820699461662392</v>
       </c>
       <c r="G31">
-        <v>0.0004848051049100107</v>
+        <v>0.000482462048187664</v>
       </c>
       <c r="H31">
-        <v>0.0004773219482563297</v>
+        <v>0.0004742929542496566</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4.50830138144935E-08</v>
+        <v>6.659111135089544E-08</v>
       </c>
       <c r="E32">
-        <v>0.004598333601472889</v>
+        <v>0.004598347889379817</v>
       </c>
       <c r="F32">
-        <v>0.004628934856331564</v>
+        <v>0.004628929983187366</v>
       </c>
       <c r="G32">
-        <v>0.004631676729955064</v>
+        <v>0.004631656525322463</v>
       </c>
       <c r="H32">
-        <v>0.004631468830993591</v>
+        <v>0.004631355744247889</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.0005173766133551512</v>
+        <v>0.0005173755178365671</v>
       </c>
       <c r="C33">
-        <v>0.0005173779144674856</v>
+        <v>0.0005173774329491241</v>
       </c>
       <c r="D33">
-        <v>0.0005173529002561323</v>
+        <v>0.000517341195756484</v>
       </c>
       <c r="E33">
-        <v>0.0005029193066897798</v>
+        <v>0.0005028913493355631</v>
       </c>
       <c r="F33">
-        <v>0.0005156596912865</v>
+        <v>0.0005156384550913163</v>
       </c>
       <c r="G33">
-        <v>0.0005173350188685902</v>
+        <v>0.0005173162486479918</v>
       </c>
       <c r="H33">
-        <v>0.0005171404403562123</v>
+        <v>0.0005170419794893002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.009311622113024214</v>
+        <v>0.009317947752843607</v>
       </c>
       <c r="E36">
-        <v>2.008322572058651</v>
+        <v>1.971130302544309</v>
       </c>
       <c r="F36">
-        <v>1.901688756686244</v>
+        <v>1.840868496852326</v>
       </c>
       <c r="G36">
-        <v>1.877472852013478</v>
+        <v>1.772101755185624</v>
       </c>
       <c r="H36">
-        <v>1.850777235803979</v>
+        <v>1.774981007915863</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4.765218700487397E-09</v>
+        <v>7.020008087909509E-09</v>
       </c>
       <c r="C38">
-        <v>2.079729892645632E-09</v>
+        <v>3.067815101256366E-09</v>
       </c>
       <c r="D38">
-        <v>0.00455767278883643</v>
+        <v>0.004550072076126696</v>
       </c>
       <c r="E38">
-        <v>0.375322724034962</v>
+        <v>0.4126014701999849</v>
       </c>
       <c r="F38">
-        <v>0.4819143571720141</v>
+        <v>0.5428833855656737</v>
       </c>
       <c r="G38">
-        <v>0.506127323155061</v>
+        <v>0.6116027035982079</v>
       </c>
       <c r="H38">
-        <v>0.5328429307245841</v>
+        <v>0.6086614491435218</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.335035615147384E-08</v>
+        <v>4.919265312950091E-08</v>
       </c>
       <c r="C40">
-        <v>1.918727058282095E-08</v>
+        <v>2.829914674457308E-08</v>
       </c>
       <c r="D40">
-        <v>0.005533453055858512</v>
+        <v>0.005539994886874022</v>
       </c>
       <c r="E40">
-        <v>0.7005756025800204</v>
+        <v>0.7908056212937384</v>
       </c>
       <c r="F40">
-        <v>0.8257601652862163</v>
+        <v>0.9451920569714017</v>
       </c>
       <c r="G40">
-        <v>0.8763212595839197</v>
+        <v>1.040556076107498</v>
       </c>
       <c r="H40">
-        <v>0.8995068337931024</v>
+        <v>0.9690980590623599</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2.834780273097461E-08</v>
+        <v>4.181375516187582E-08</v>
       </c>
       <c r="C41">
-        <v>1.630917999761965E-08</v>
+        <v>2.405427473468719E-08</v>
       </c>
       <c r="D41">
-        <v>0.004703435097479719</v>
+        <v>0.004708995653843446</v>
       </c>
       <c r="E41">
-        <v>0.5954892621991091</v>
+        <v>0.6721847780995696</v>
       </c>
       <c r="F41">
-        <v>0.7018961404902916</v>
+        <v>0.8034132484252966</v>
       </c>
       <c r="G41">
-        <v>0.7448730706464598</v>
+        <v>0.8844726646910651</v>
       </c>
       <c r="H41">
-        <v>0.7645808087238666</v>
+        <v>0.8237333502030117</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.002553420499221E-09</v>
+        <v>-7.378897967625094E-09</v>
       </c>
       <c r="C42">
-        <v>-2.878090585201292E-09</v>
+        <v>-4.244872009885898E-09</v>
       </c>
       <c r="D42">
-        <v>-0.0008300179583787927</v>
+        <v>-0.0008309992330305764</v>
       </c>
       <c r="E42">
-        <v>-0.1050863403809112</v>
+        <v>-0.1186208431941689</v>
       </c>
       <c r="F42">
-        <v>-0.1238640247959247</v>
+        <v>-0.1417788085461051</v>
       </c>
       <c r="G42">
-        <v>-0.1314481889374599</v>
+        <v>-0.156083411416433</v>
       </c>
       <c r="H42">
-        <v>-0.1349260250692358</v>
+        <v>-0.1453647088593482</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-1.981980716243111</v>
+        <v>-1.931167473094821</v>
       </c>
       <c r="F43">
-        <v>-1.851994001369368</v>
+        <v>-1.773110193750054</v>
       </c>
       <c r="G43">
-        <v>-1.81527682960267</v>
+        <v>-1.685166231870543</v>
       </c>
       <c r="H43">
-        <v>-1.777188737257294</v>
+        <v>-1.690917830305701</v>
       </c>
     </row>
     <row r="44" spans="1:8">
